--- a/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\template_state_3.3\elec\GDPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AL\elec\GDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029EB199-BDFD-4E2A-909C-05D530040DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAEE0C19-1ED7-4BCA-904C-4263ADBC6EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1440" windowWidth="14400" windowHeight="7455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,130 +35,130 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>The values in this variable are intended to be set by the model user to represent the</t>
+  </si>
+  <si>
+    <t>policy he/she wishes to simulate using this lever.  Accordingly, there is no</t>
+  </si>
+  <si>
+    <t>source information here.</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>solar PV</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>This variable is used to specify the percentage of potential electricity output from each</t>
+  </si>
+  <si>
+    <t>As an example, we provide an "environmentally preferred" set of contracted dispatch</t>
+  </si>
+  <si>
+    <t>percentages, where wind and solar have a large percentage of their output covered by</t>
+  </si>
+  <si>
+    <t>contracts, and coal has none (e.g. coal is only dispatched during the least-cost dispatch</t>
+  </si>
+  <si>
+    <t>phase).</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
+  </si>
+  <si>
     <t>GDPbES Guaranteed Dispatch Percentage by Electricity Source</t>
   </si>
   <si>
+    <t>source that is guaranteed (e.g. dispatched before any least-cost dispatching</t>
+  </si>
+  <si>
+    <t>begins) when "Boolean Use Non BAU Guaranteed Dispatch Settings" is enabled.</t>
+  </si>
+  <si>
+    <t>Some dispatch from peaking plants (natural gas peakers and petroleum-fired plants)</t>
+  </si>
+  <si>
+    <t>is guaranteed in the model, to provide for grid stability and regulation needs.</t>
+  </si>
+  <si>
+    <t>The model will disatch these plants in the guaranteed dispatch section by the larger</t>
+  </si>
+  <si>
+    <t>of the default amount or the amount specified here by the user.</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>Guaranteed Dispatch Fraction (dimensionless)</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
+  </si>
+  <si>
     <t>Alabama</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>This variable is used to specify the percentage of potential electricity output from each</t>
-  </si>
-  <si>
-    <t>source that is guaranteed (e.g. dispatched before any least-cost dispatching</t>
-  </si>
-  <si>
-    <t>begins) when "Boolean Use Non BAU Guaranteed Dispatch Settings" is enabled.</t>
-  </si>
-  <si>
-    <t>The values in this variable are intended to be set by the model user to represent the</t>
-  </si>
-  <si>
-    <t>policy he/she wishes to simulate using this lever.  Accordingly, there is no</t>
-  </si>
-  <si>
-    <t>source information here.</t>
-  </si>
-  <si>
-    <t>As an example, we provide an "environmentally preferred" set of contracted dispatch</t>
-  </si>
-  <si>
-    <t>percentages, where wind and solar have a large percentage of their output covered by</t>
-  </si>
-  <si>
-    <t>contracts, and coal has none (e.g. coal is only dispatched during the least-cost dispatch</t>
-  </si>
-  <si>
-    <t>phase).</t>
-  </si>
-  <si>
-    <t>Some dispatch from peaking plants (natural gas peakers and petroleum-fired plants)</t>
-  </si>
-  <si>
-    <t>is guaranteed in the model, to provide for grid stability and regulation needs.</t>
-  </si>
-  <si>
-    <t>The model will disatch these plants in the guaranteed dispatch section by the larger</t>
-  </si>
-  <si>
-    <t>of the default amount or the amount specified here by the user.</t>
-  </si>
-  <si>
-    <t>Guaranteed Dispatch Fraction (dimensionless)</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>solar PV</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>natural gas peaker</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>offshore wind</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>hard coal w CCS</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle w CCS</t>
-  </si>
-  <si>
-    <t>biomass w CCS</t>
-  </si>
-  <si>
-    <t>lignite w CCS</t>
-  </si>
-  <si>
-    <t>small modular reactor</t>
-  </si>
-  <si>
-    <t>hydrogen combustion turbine</t>
-  </si>
-  <si>
-    <t>hydrogen combined cycle</t>
   </si>
 </sst>
 </file>
@@ -532,93 +531,93 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C1" s="5">
-        <v>45194</v>
+        <v>45237</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -634,9 +633,9 @@
     <col min="2" max="2" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="45" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:37" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B1" s="2">
         <v>2015</v>
@@ -749,17 +748,17 @@
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:L15" si="0">$B2</f>
+        <f>$B2</f>
         <v>0</v>
       </c>
       <c r="D2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D2:AK10" si="0">$B2</f>
         <v>0</v>
       </c>
       <c r="E2">
@@ -795,151 +794,151 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <f t="shared" ref="M2:V15" si="1">$B2</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W2">
-        <f t="shared" ref="W2:AK15" si="2">$B2</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AI2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AK2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <f t="shared" si="0"/>
+        <f>$B3</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D3:AK4" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M3">
@@ -983,111 +982,111 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <f t="shared" si="0"/>
+        <f>$B4</f>
         <v>0</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M4">
@@ -1131,75 +1130,75 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>0.5</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C5:C15" si="2">$B5</f>
         <v>0.5</v>
       </c>
       <c r="D5">
@@ -1239,115 +1238,115 @@
         <v>0.5</v>
       </c>
       <c r="M5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="N5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="O5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="P5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="R5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="S5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="T5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="U5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="V5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="W5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="X5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AD5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AE5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AG5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AH5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AI5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AJ5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AK5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>0.5</v>
       </c>
       <c r="C6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="D6">
@@ -1387,115 +1386,115 @@
         <v>0.5</v>
       </c>
       <c r="M6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="P6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="R6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="S6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="T6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="U6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="V6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="W6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="X6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AG6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AJ6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>0.8</v>
       </c>
       <c r="C7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="D7">
@@ -1535,115 +1534,115 @@
         <v>0.8</v>
       </c>
       <c r="M7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="P7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="R7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="S7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="T7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="U7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="V7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="W7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="X7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AG7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AH7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AI7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AJ7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>0.8</v>
       </c>
       <c r="C8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="D8">
@@ -1683,115 +1682,115 @@
         <v>0.8</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="O8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="P8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="R8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="S8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="T8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="U8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="V8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="W8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="X8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AJ8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AK8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>0.8</v>
       </c>
       <c r="C9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="D9">
@@ -1831,115 +1830,115 @@
         <v>0.8</v>
       </c>
       <c r="M9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="P9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="R9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="S9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="T9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="U9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="V9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="W9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="X9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="Z9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AD9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AI9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AJ9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AK9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>0.5</v>
       </c>
       <c r="C10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="D10">
@@ -1979,1296 +1978,1296 @@
         <v>0.5</v>
       </c>
       <c r="M10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="P10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="R10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="S10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="T10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="U10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="V10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="W10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="X10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D10:AK15" si="3">$B10</f>
         <v>0.5</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0.8</v>
       </c>
       <c r="C11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="D11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="F11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="G11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="H11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="I11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="J11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="K11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="M11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="P11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="R11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="S11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="T11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="U11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="V11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="W11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="X11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
-        <f t="shared" ref="B16:AK16" si="3">B12</f>
+        <f>B12</f>
         <v>0</v>
       </c>
       <c r="C16">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="C16:AK16" si="4">C12</f>
         <v>0</v>
       </c>
       <c r="D16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AI16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
-        <f t="shared" ref="B17:AK17" si="4">B12</f>
+        <f>B12</f>
         <v>0</v>
       </c>
       <c r="C17">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="C17:AK17" si="5">C12</f>
         <v>0</v>
       </c>
       <c r="D17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AH17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AI17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AJ17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AK17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
-        <f t="shared" ref="B18:AK18" si="5">B10</f>
+        <f>B10</f>
         <v>0.5</v>
       </c>
       <c r="C18">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C18:AK18" si="6">C10</f>
         <v>0.5</v>
       </c>
       <c r="D18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="F18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="G18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="H18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="I18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="J18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="K18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="L18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="M18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="N18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="O18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="P18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="R18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="S18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="T18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="U18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="V18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="W18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="X18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Z18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AC18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AD18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AE18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AF18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AG18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AH18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AI18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AJ18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="AK18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3381,7 +3380,7 @@
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3494,7 +3493,7 @@
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3607,7 +3606,7 @@
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3720,7 +3719,7 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3833,7 +3832,7 @@
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A24" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3946,7 +3945,7 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.75">
       <c r="A25" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25">
         <v>0</v>

--- a/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AL\elec\GDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAEE0C19-1ED7-4BCA-904C-4263ADBC6EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A3B5A7F-7042-4A1F-9BEC-643F5DE092E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="720" windowWidth="14480" windowHeight="10080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -527,9 +527,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -537,80 +537,80 @@
         <v>41</v>
       </c>
       <c r="C1" s="5">
-        <v>45237</v>
+        <v>45294</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -627,13 +627,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.40625" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:37" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -746,7 +746,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>40</v>
       </c>

--- a/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AL\elec\GDPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\AL\elec\GDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A3B5A7F-7042-4A1F-9BEC-643F5DE092E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85CDF4F7-04D7-45BE-A07E-00BBFC5BD36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="720" windowWidth="14480" windowHeight="10080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -537,7 +537,7 @@
         <v>41</v>
       </c>
       <c r="C1" s="5">
-        <v>45294</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
